--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-08.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-08.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,27 +833,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -864,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -891,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -918,17 +922,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -945,27 +949,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,23 +976,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1003,24 +1007,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>3</v>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,31 +1949,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1984,23 +1984,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2015,27 +2015,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2050,31 +2050,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2120,27 +2120,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2155,27 +2151,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>395.1</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2298,23 +2298,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>174.9</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -2352,17 +2352,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>395.1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2379,17 +2379,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>174.9</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2712,20 +2712,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>3</v>
@@ -2739,27 +2743,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2770,17 +2770,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2797,23 +2797,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2824,23 +2828,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2851,17 +2859,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2878,27 +2886,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -2909,24 +2913,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>3</v>
@@ -3171,17 +3171,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3198,17 +3198,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3336,31 +3336,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3367,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>212K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3406,27 +3402,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -3441,27 +3437,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3472,27 +3472,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -3507,23 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -3538,27 +3538,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -3573,27 +3569,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>182K</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -3608,27 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>25K</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3674,31 +3674,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3709,23 +3705,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -3740,23 +3736,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -3771,27 +3767,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3802,23 +3802,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -4134,31 +4134,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4169,23 +4169,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4200,27 +4204,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -4231,27 +4239,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4266,31 +4270,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -4336,27 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,20 +4978,24 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
         <v>3</v>
@@ -5005,17 +5009,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,17 +5036,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5059,23 +5063,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2.60M</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -5086,27 +5094,23 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>-1.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
@@ -5117,27 +5121,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -5148,17 +5148,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5175,17 +5175,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5202,27 +5202,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1.1M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -5336,31 +5336,23 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -5371,27 +5363,23 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5406,27 +5394,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5441,27 +5429,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5476,23 +5464,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -5503,17 +5499,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -5530,31 +5526,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>22.20</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -5565,23 +5553,23 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5596,27 +5584,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -5631,23 +5619,23 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -5662,21 +5650,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+          <t>1.4%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5689,23 +5685,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -5716,31 +5720,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -5751,31 +5755,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>203K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -5786,31 +5790,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-10.9</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5821,27 +5817,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -5852,17 +5852,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>22.20</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -6282,27 +6282,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -6333,7 +6333,7 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -6348,31 +6348,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -6383,23 +6379,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -6414,31 +6414,31 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>4.070%</t>
+          <t>4.210%</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -6688,17 +6688,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>4.210%</t>
+          <t>4.070%</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6993,27 +6993,23 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -7063,23 +7059,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
+          <t>1853K</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,23 +7268,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -7295,17 +7299,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7322,27 +7326,23 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.021M</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -7353,20 +7353,24 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
         <v>3</v>
@@ -7380,24 +7384,20 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
         <v>3</v>
@@ -7411,23 +7411,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -7438,17 +7442,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>7.04%</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7465,17 +7469,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7492,27 +7496,23 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7705,27 +7705,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -7740,31 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7775,27 +7775,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7806,31 +7810,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7841,31 +7845,31 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -7876,27 +7880,23 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>73.2</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8632,31 +8632,31 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -8667,27 +8667,31 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr"/>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -8698,23 +8702,23 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -8729,27 +8733,23 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -8764,23 +8764,23 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -8795,23 +8795,23 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -8965,23 +8965,23 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -8992,17 +8992,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -9019,17 +9019,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -9046,17 +9046,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -9073,23 +9073,23 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>163</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,27 +9228,23 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.043M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -9259,24 +9255,20 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
@@ -9290,23 +9282,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -9317,23 +9313,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -9344,27 +9344,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -9375,20 +9371,24 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>3</v>
@@ -9402,17 +9402,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,23 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -9568,23 +9572,23 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -9599,23 +9603,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
           <t>2.3%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>1.1%</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -9630,27 +9638,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9665,7 +9673,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9675,21 +9683,17 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -9700,27 +9704,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9735,31 +9739,31 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -9770,27 +9774,23 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -9933,17 +9933,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -9960,17 +9960,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
+          <t>4.240%</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
           <t>4.250%</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>4.265%</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -10068,31 +10068,31 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -10103,31 +10103,31 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -10138,31 +10138,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -10173,25 +10169,13 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
         <v>2</v>
       </c>
@@ -10204,12 +10188,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -10219,16 +10203,16 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -10239,31 +10223,31 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -10274,31 +10258,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -10309,15 +10289,31 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
+          <t>Core PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="G334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -10328,23 +10324,27 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr"/>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -10359,31 +10359,31 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,23 +11182,23 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -11209,23 +11209,23 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -11236,17 +11236,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,31 +11561,27 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -11596,23 +11592,23 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G379" t="n">
@@ -11627,23 +11623,23 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -11658,27 +11654,31 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -11689,17 +11689,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -11716,17 +11716,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -11770,22 +11770,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -11801,27 +11801,27 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -11832,17 +11832,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -11859,24 +11859,20 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
         <v>3</v>
@@ -11890,17 +11886,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -11917,23 +11913,27 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -12040,27 +12040,23 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1850K</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G395" t="n">
@@ -12075,27 +12071,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G396" t="n">
@@ -12145,27 +12141,27 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>208K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G398" t="n">
@@ -12180,23 +12176,27 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
+          <t>1850K</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G399" t="n">
@@ -12442,27 +12442,31 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
+          <t>307K</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>170K</t>
+        </is>
+      </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -12473,31 +12477,31 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -12508,27 +12512,31 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -12539,27 +12547,27 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G412" t="n">
@@ -12574,27 +12582,31 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -12605,31 +12617,27 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -12640,27 +12648,27 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G415" t="n">
@@ -12675,31 +12683,31 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -12710,27 +12718,23 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -12745,31 +12749,27 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -12872,27 +12872,23 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G423" t="n">
@@ -12907,31 +12903,31 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -12942,23 +12938,27 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="G425" t="n">
@@ -12973,27 +12973,23 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G426" t="n">
@@ -13008,23 +13004,27 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G427" t="n">
@@ -13039,31 +13039,31 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G428" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="429">
@@ -13636,31 +13636,31 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -13671,31 +13671,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -13706,27 +13702,27 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G453" t="n">
@@ -13741,27 +13737,27 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -13776,27 +13772,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -13807,31 +13807,31 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
@@ -13869,17 +13869,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13896,23 +13896,27 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -13923,27 +13927,23 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -13954,20 +13954,24 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="n">
         <v>3</v>
@@ -13981,27 +13985,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14012,17 +14012,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14039,24 +14039,20 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="n">
         <v>3</v>
@@ -14070,23 +14066,27 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -14224,23 +14224,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -14255,27 +14259,23 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -14290,19 +14290,19 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14310,11 +14310,11 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -14325,27 +14325,31 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr"/>
+          <t>220K</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>215K</t>
+        </is>
+      </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -14356,27 +14360,27 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G475" t="n">
@@ -14391,31 +14395,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -14426,31 +14426,31 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -14461,19 +14461,19 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
           <t>3.5%</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>3.2%</t>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G478" t="n">
@@ -14496,31 +14496,27 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -14531,23 +14527,27 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -14728,31 +14728,27 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -14763,23 +14759,23 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G488" t="n">
@@ -14794,22 +14790,22 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -14829,31 +14825,27 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -14864,31 +14856,27 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E491" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -14899,27 +14887,31 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -14930,22 +14922,22 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -14965,27 +14957,31 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -14996,27 +14992,31 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E495" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G495" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -15027,27 +15027,31 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -15058,23 +15062,23 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G497" t="n">
@@ -15089,27 +15093,23 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="G498" t="n">
@@ -15124,27 +15124,27 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G499" t="n">
@@ -15159,31 +15159,31 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="G500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -15194,31 +15194,31 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Business Inventories MoMDEC</t>
+          <t>Retail Inventories Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -15229,31 +15229,31 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMDEC</t>
+          <t>Business Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E502" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F502" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
       <c r="G502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -15483,17 +15483,17 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>4.220%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>4.185%</t>
+          <t>4.225%</t>
         </is>
       </c>
       <c r="E512" t="inlineStr"/>
@@ -15510,17 +15510,17 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.220%</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>4.225%</t>
+          <t>4.185%</t>
         </is>
       </c>
       <c r="E513" t="inlineStr"/>
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15768,17 +15768,17 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E523" t="inlineStr"/>
@@ -15795,23 +15795,23 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
       <c r="F524" t="inlineStr"/>
       <c r="G524" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="525">
@@ -15822,17 +15822,17 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
@@ -16510,17 +16510,17 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E549" t="inlineStr"/>
@@ -16537,17 +16537,17 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E550" t="inlineStr"/>
@@ -16984,27 +16984,27 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G567" t="n">
@@ -17019,24 +17019,20 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -17054,23 +17050,27 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr"/>
+          <t>51.2</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G569" t="n">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>592</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>588</t>
         </is>
       </c>
       <c r="E579" t="inlineStr"/>
@@ -17391,17 +17391,17 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>487</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>481</t>
         </is>
       </c>
       <c r="E580" t="inlineStr"/>
@@ -17649,23 +17649,19 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E590" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr"/>
       <c r="F590" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G590" t="n">
@@ -17839,19 +17835,23 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G596" t="n">
@@ -17901,19 +17901,19 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G598" t="n">
@@ -17928,19 +17928,19 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G599" t="n">
@@ -17955,23 +17955,27 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="E600" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -17982,23 +17986,19 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E601" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr"/>
       <c r="F601" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G601" t="n">
@@ -18013,19 +18013,23 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E602" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="G602" t="n">
@@ -18040,27 +18044,23 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -18668,19 +18668,19 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="628">
@@ -18714,19 +18714,19 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E629" t="inlineStr"/>
       <c r="F629" t="inlineStr"/>
       <c r="G629" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="630">
@@ -18821,23 +18821,19 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>0.698M</t>
-        </is>
-      </c>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>0.68M</t>
-        </is>
-      </c>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr"/>
       <c r="F634" t="inlineStr">
         <is>
-          <t>0.68M</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="G634" t="n">
@@ -18910,19 +18906,23 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="E637" t="inlineStr"/>
+          <t>0.698M</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>0.68M</t>
+        </is>
+      </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.68M</t>
         </is>
       </c>
       <c r="G637" t="n">
@@ -19375,13 +19375,13 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E656" t="inlineStr"/>
@@ -19444,13 +19444,13 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="E659" t="inlineStr"/>
@@ -19505,23 +19505,23 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G662" t="n">
@@ -19536,25 +19536,17 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="E663" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F663" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
       <c r="G663" t="n">
         <v>3</v>
       </c>
@@ -19652,17 +19644,25 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E667" t="inlineStr"/>
-      <c r="F667" t="inlineStr"/>
+          <t>1.482M</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="G667" t="n">
         <v>3</v>
       </c>
@@ -19946,13 +19946,13 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -19966,7 +19966,7 @@
         </is>
       </c>
       <c r="G677" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="678">
@@ -20070,23 +20070,19 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E681" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr"/>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G681" t="n">
@@ -20101,19 +20097,23 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E682" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G682" t="n">
@@ -20128,27 +20128,27 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="684">
@@ -20159,27 +20159,23 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr"/>
       <c r="F684" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">
@@ -20221,27 +20217,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="687">
@@ -20252,23 +20248,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E687" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -20279,27 +20279,23 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr"/>
       <c r="F688" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G688" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="689">
@@ -20310,23 +20306,23 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ 2nd EstQ4</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -20341,23 +20337,27 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="E690" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G690" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="691">
@@ -21228,27 +21228,27 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G727" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="728">
@@ -21410,23 +21410,23 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G733" t="n">
@@ -21441,27 +21441,27 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G734" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="735">
@@ -21472,27 +21472,27 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="736">
@@ -21534,27 +21534,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="738">
@@ -21565,27 +21565,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="739">
@@ -21596,27 +21596,27 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G739" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="740">
@@ -21716,27 +21716,27 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G743" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="744">
@@ -22471,16 +22471,16 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>LMI Logistics Managers IndexFEB</t>
+          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
-      <c r="D772" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="E772" t="inlineStr"/>
+      <c r="D772" t="inlineStr"/>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="F772" t="inlineStr"/>
       <c r="G772" t="n">
         <v>3</v>
@@ -22494,16 +22494,16 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 6 to 10 yrs</t>
+          <t>LMI Logistics Managers IndexFEB</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
-      <c r="D773" t="inlineStr"/>
-      <c r="E773" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr"/>
       <c r="F773" t="inlineStr"/>
       <c r="G773" t="n">
         <v>3</v>
@@ -22669,7 +22669,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/28</t>
+          <t>MBA Purchase IndexFEB/28</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -22688,7 +22688,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/28</t>
+          <t>MBA Mortgage ApplicationsFEB/28</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22726,7 +22726,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA Mortgage Refinance IndexFEB/28</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -22934,23 +22934,23 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders MoMJAN</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E793" t="inlineStr"/>
       <c r="F793" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G793" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="794">
@@ -22961,19 +22961,19 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E794" t="inlineStr"/>
       <c r="F794" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G794" t="n">
@@ -23150,19 +23150,19 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23177,19 +23177,19 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G802" t="n">
@@ -23204,19 +23204,19 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
       <c r="D803" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G803" t="n">
@@ -23231,23 +23231,23 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Factory Orders MoMJAN</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E804" t="inlineStr"/>
       <c r="F804" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G804" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="805">
@@ -23380,7 +23380,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
@@ -23399,7 +23399,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
@@ -23589,7 +23589,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
@@ -23669,15 +23669,11 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C826" t="inlineStr"/>
-      <c r="D826" t="inlineStr">
-        <is>
-          <t>15.6M</t>
-        </is>
-      </c>
+      <c r="D826" t="inlineStr"/>
       <c r="E826" t="inlineStr"/>
       <c r="F826" t="inlineStr"/>
       <c r="G826" t="n">
@@ -23692,11 +23688,15 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C827" t="inlineStr"/>
-      <c r="D827" t="inlineStr"/>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>15.6M</t>
+        </is>
+      </c>
       <c r="E827" t="inlineStr"/>
       <c r="F827" t="inlineStr"/>
       <c r="G827" t="n">
@@ -23918,15 +23918,27 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C837" t="inlineStr"/>
-      <c r="D837" t="inlineStr"/>
-      <c r="E837" t="inlineStr"/>
-      <c r="F837" t="inlineStr"/>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="G837" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="838">
@@ -23964,23 +23976,23 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C839" t="inlineStr"/>
       <c r="D839" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E839" t="inlineStr"/>
       <c r="F839" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G839" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="840">
@@ -23991,23 +24003,15 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
+      <c r="D840" t="inlineStr"/>
       <c r="E840" t="inlineStr"/>
-      <c r="F840" t="inlineStr">
-        <is>
-          <t>$-103B</t>
-        </is>
-      </c>
+      <c r="F840" t="inlineStr"/>
       <c r="G840" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="841">
@@ -24018,23 +24022,15 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
-      <c r="D841" t="inlineStr">
-        <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
+      <c r="D841" t="inlineStr"/>
       <c r="E841" t="inlineStr"/>
-      <c r="F841" t="inlineStr">
-        <is>
-          <t>$376.0B</t>
-        </is>
-      </c>
+      <c r="F841" t="inlineStr"/>
       <c r="G841" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="842">
@@ -24099,27 +24095,15 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E844" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="F844" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D844" t="inlineStr"/>
+      <c r="E844" t="inlineStr"/>
+      <c r="F844" t="inlineStr"/>
       <c r="G844" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="845">
@@ -24130,15 +24114,23 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
-      <c r="D845" t="inlineStr"/>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
       <c r="E845" t="inlineStr"/>
-      <c r="F845" t="inlineStr"/>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>$-103B</t>
+        </is>
+      </c>
       <c r="G845" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="846">
@@ -24149,15 +24141,23 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
-      <c r="D846" t="inlineStr"/>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
       <c r="E846" t="inlineStr"/>
-      <c r="F846" t="inlineStr"/>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>$376.0B</t>
+        </is>
+      </c>
       <c r="G846" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="847">
@@ -24168,23 +24168,23 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C847" t="inlineStr"/>
       <c r="D847" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="E847" t="inlineStr"/>
       <c r="F847" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>$273.0B</t>
         </is>
       </c>
       <c r="G847" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="848">
@@ -24461,23 +24461,23 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
       <c r="D862" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr">
         <is>
-          <t>180.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G862" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="863">
@@ -24596,23 +24596,23 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Nonfarm Payrolls PrivateFEB</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
       <c r="D867" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="E867" t="inlineStr"/>
       <c r="F867" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>170.0K</t>
         </is>
       </c>
       <c r="G867" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="868">
@@ -24650,23 +24650,23 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="E869" t="inlineStr"/>
       <c r="F869" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>180.0K</t>
         </is>
       </c>
       <c r="G869" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="870">
@@ -24727,23 +24727,23 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsFEB</t>
+          <t>Participation RateFEB</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
       <c r="D872" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="E872" t="inlineStr"/>
       <c r="F872" t="inlineStr">
         <is>
-          <t>6.0K</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="G872" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="873">
@@ -24781,19 +24781,19 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Government PayrollsFEB</t>
+          <t>Manufacturing PayrollsFEB</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
       <c r="D874" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>-20.0K</t>
+          <t>6.0K</t>
         </is>
       </c>
       <c r="G874" t="n">
@@ -24808,23 +24808,23 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>Government PayrollsFEB</t>
         </is>
       </c>
       <c r="C875" t="inlineStr"/>
       <c r="D875" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="E875" t="inlineStr"/>
       <c r="F875" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>-20.0K</t>
         </is>
       </c>
       <c r="G875" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="876">
@@ -24889,19 +24889,23 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C878" t="inlineStr"/>
       <c r="D878" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E878" t="inlineStr"/>
-      <c r="F878" t="inlineStr"/>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="G878" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="879">
@@ -24912,23 +24916,23 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
       <c r="D879" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
       <c r="F879" t="inlineStr">
         <is>
-          <t>170.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G879" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="880">
@@ -24993,23 +24997,19 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
       <c r="D882" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E882" t="inlineStr"/>
-      <c r="F882" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="F882" t="inlineStr"/>
       <c r="G882" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="883">
